--- a/engine/eval/fixtures/holdout_labels_blank.xlsx
+++ b/engine/eval/fixtures/holdout_labels_blank.xlsx
@@ -6137,7 +6137,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Choose the single primary complaint archetype, not every issue mentioned.</t>
+          <t>Choose the single primary complaint archetype, not every issue mentioned. TIE-BREAK: if a product defect causes the hazard, safety_health beats product_fault.</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Choose the single primary complaint archetype, not every issue mentioned.</t>
+          <t>Choose the single primary complaint archetype, not every issue mentioned. TIE-BREAK: an unauthorised/not-mine entry is fraud_security, not record_accuracy.</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Choose the single primary complaint archetype, not every issue mentioned.</t>
+          <t>Choose the single primary complaint archetype, not every issue mentioned. TIE-BREAK: deception into a charge is misleading_practice; a wrong amount is billing_charge.</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone.</t>
+          <t>Use the first explicitly requested remedy. Do not infer a remedy from dissatisfaction alone. Only a request made IN THIS message counts, not one merely recounted as previously asked.</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Choose the main severity driver. Do not upgrade normal inconvenience into severe harm.</t>
+          <t>Choose the main severity driver. Do not upgrade normal inconvenience into severe harm. NO minimum: any disputed sum counts (a small fee included) — never 'none' because it is small.</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Label the writer's tone independently from severity.</t>
+          <t>Label the writer's tone independently from severity. Adjacent tones: calm(no worry) -&gt; concerned(worry) -&gt; frustrated(dissatisfaction) -&gt; angry(hostility outward); distressed = fear/strain inward.</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Label the writer's tone independently from severity.</t>
+          <t>Label the writer's tone independently from severity. Adjacent tones: calm(no worry) -&gt; concerned(worry) -&gt; frustrated(dissatisfaction) -&gt; angry(hostility outward); distressed = fear/strain inward.</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Label the writer's tone independently from severity.</t>
+          <t>Label the writer's tone independently from severity. Adjacent tones: calm(no worry) -&gt; concerned(worry) -&gt; frustrated(dissatisfaction) -&gt; angry(hostility outward); distressed = fear/strain inward.</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Label the writer's tone independently from severity.</t>
+          <t>Label the writer's tone independently from severity. Adjacent tones: calm(no worry) -&gt; concerned(worry) -&gt; frustrated(dissatisfaction) -&gt; angry(hostility outward); distressed = fear/strain inward.</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Label the writer's tone independently from severity.</t>
+          <t>Label the writer's tone independently from severity. Adjacent tones: calm(no worry) -&gt; concerned(worry) -&gt; frustrated(dissatisfaction) -&gt; angry(hostility outward); distressed = fear/strain inward.</t>
         </is>
       </c>
     </row>
